--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2011,6 +2011,829 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128713631</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57683</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>337452</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6433667</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128707280</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102827</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>337402</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6433652</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128708259</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>337402</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433654</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128705785</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58059</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>337448</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433666</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128710377</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57847</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>337388</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6433650</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128712441</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89714</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>595</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lilanopping</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Entoloma euchroum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pers.) Donk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>337359</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6433642</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Skogssänka med al, blandskog</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128706443</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>337403</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433662</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På död granstamm födosökande</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102827</v>
+        <v>102829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102829</v>
+        <v>102835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102835</v>
+        <v>102836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2016,7 +2016,7 @@
         <v>128713631</v>
       </c>
       <c r="B13" t="n">
-        <v>57683</v>
+        <v>57710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102836</v>
+        <v>102863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128708259</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>128705785</v>
       </c>
       <c r="B16" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128710377</v>
       </c>
       <c r="B17" t="n">
-        <v>57847</v>
+        <v>57874</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128712441</v>
       </c>
       <c r="B18" t="n">
-        <v>89714</v>
+        <v>89741</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128706443</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102863</v>
+        <v>102869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128712441</v>
       </c>
       <c r="B18" t="n">
-        <v>89741</v>
+        <v>89746</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102869</v>
+        <v>102876</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128712441</v>
       </c>
       <c r="B18" t="n">
-        <v>89746</v>
+        <v>89751</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2016,7 +2016,7 @@
         <v>128713631</v>
       </c>
       <c r="B13" t="n">
-        <v>57710</v>
+        <v>57714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102876</v>
+        <v>102880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128708259</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>128705785</v>
       </c>
       <c r="B16" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128710377</v>
       </c>
       <c r="B17" t="n">
-        <v>57874</v>
+        <v>57878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128712441</v>
       </c>
       <c r="B18" t="n">
-        <v>89751</v>
+        <v>89755</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128706443</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2016,7 +2016,7 @@
         <v>128713631</v>
       </c>
       <c r="B13" t="n">
-        <v>57714</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102880</v>
+        <v>102887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128708259</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>128705785</v>
       </c>
       <c r="B16" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128710377</v>
       </c>
       <c r="B17" t="n">
-        <v>57878</v>
+        <v>57881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128712441</v>
       </c>
       <c r="B18" t="n">
-        <v>89755</v>
+        <v>89760</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128706443</v>
       </c>
       <c r="B19" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102895</v>
+        <v>102900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128712441</v>
       </c>
       <c r="B18" t="n">
-        <v>89767</v>
+        <v>89770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102900</v>
+        <v>102903</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128712441</v>
       </c>
       <c r="B18" t="n">
-        <v>89770</v>
+        <v>89773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2016,7 +2016,7 @@
         <v>128713631</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>57719</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102903</v>
+        <v>102913</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128708259</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>128705785</v>
       </c>
       <c r="B16" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128710377</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128712441</v>
       </c>
       <c r="B18" t="n">
-        <v>89773</v>
+        <v>89777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128706443</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22637-2025 artfynd.xlsx
+++ b/artfynd/A 22637-2025 artfynd.xlsx
@@ -2016,7 +2016,7 @@
         <v>128713631</v>
       </c>
       <c r="B13" t="n">
-        <v>57719</v>
+        <v>57721</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>128707280</v>
       </c>
       <c r="B14" t="n">
-        <v>102913</v>
+        <v>102922</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128708259</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>128705785</v>
       </c>
       <c r="B16" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128710377</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128712441</v>
       </c>
       <c r="B18" t="n">
-        <v>89777</v>
+        <v>89786</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128706443</v>
       </c>
       <c r="B19" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
